--- a/employee_information_forms/035_uniform_distribution_form--employee_information_forms.xlsx
+++ b/employee_information_forms/035_uniform_distribution_form--employee_information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -557,7 +557,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Format: mm/dd/yyyy</t>
+          <t>Format - mm/dd/yyyy</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Distribution Date</t>
+          <t>Date In</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Format: mm/dd/yyyy</t>
+          <t>Format - mm/dd/yyyy</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Distribution Date</t>
+          <t>Distribution Date (3)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Format: mm/dd/yyyy</t>
+          <t>Format - mm/dd/yyyy</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Distribution Date</t>
+          <t>Distribution Date In</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Format: mm/dd/yyyy</t>
+          <t>Format - mm/dd/yyyy</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>employee_name</t>
+          <t>employee_name_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Employee Name</t>
+          <t>Employee Name 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Department 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>distribution_type</t>
+          <t>distribution_type_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Distribution Type</t>
+          <t>Distribution Type 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>status_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Status 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1197,7 +1197,7 @@
   <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1494,7 +1494,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1528,7 +1528,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1545,7 +1545,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1613,7 +1613,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>distribution_type_choices</t>
+          <t>distribution_type_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1630,7 +1630,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>distribution_type_choices</t>
+          <t>distribution_type_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1647,7 +1647,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>distribution_type_choices</t>
+          <t>distribution_type_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>status_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>status_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1698,7 +1698,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>status_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
